--- a/2024/tmp/CCA Junior League 4 South.xlsx
+++ b/2024/tmp/CCA Junior League 4 South.xlsx
@@ -46,7 +46,85 @@
     <t>CCA Senior League Division 1</t>
   </si>
   <si>
-    <t>117767</t>
+    <t>125381</t>
+  </si>
+  <si>
+    <t>Wilburton CC - 1st XI</t>
+  </si>
+  <si>
+    <t>60408</t>
+  </si>
+  <si>
+    <t>Audley Wenden CC - 1st XI</t>
+  </si>
+  <si>
+    <t>377531</t>
+  </si>
+  <si>
+    <t>The Piece Ground</t>
+  </si>
+  <si>
+    <t>2191</t>
+  </si>
+  <si>
+    <t>2025/05/17</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>Thriplow CC - 1st XI</t>
+  </si>
+  <si>
+    <t>51520</t>
+  </si>
+  <si>
+    <t>2025/07/12</t>
+  </si>
+  <si>
+    <t>Bluntisham CC - 1st XI</t>
+  </si>
+  <si>
+    <t>41728</t>
+  </si>
+  <si>
+    <t>2025/05/31</t>
+  </si>
+  <si>
+    <t>Fulbourn Institute CC - 1st XI</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2025/05/10</t>
+  </si>
+  <si>
+    <t>Histon CC - 2nd XI</t>
+  </si>
+  <si>
+    <t>18967</t>
+  </si>
+  <si>
+    <t>2025/08/30</t>
+  </si>
+  <si>
+    <t>Cambridge Old Monks CC - 1st XI</t>
+  </si>
+  <si>
+    <t>323460</t>
+  </si>
+  <si>
+    <t>2025/06/07</t>
+  </si>
+  <si>
+    <t>Ramsey CC, Hunts - 2nd XI</t>
+  </si>
+  <si>
+    <t>78071</t>
+  </si>
+  <si>
+    <t>2025/06/14</t>
   </si>
   <si>
     <t>Abington CC, Cambs - 1st XI</t>
@@ -55,10 +133,82 @@
     <t>29732</t>
   </si>
   <si>
-    <t>Thriplow CC - 1st XI</t>
-  </si>
-  <si>
-    <t>51520</t>
+    <t>2025/08/23</t>
+  </si>
+  <si>
+    <t>Longstanton Grasshoppers CC - 1st XI</t>
+  </si>
+  <si>
+    <t>12244</t>
+  </si>
+  <si>
+    <t>2025/07/26</t>
+  </si>
+  <si>
+    <t>Fulbourn Recreation Ground</t>
+  </si>
+  <si>
+    <t>9770</t>
+  </si>
+  <si>
+    <t>2025/07/05</t>
+  </si>
+  <si>
+    <t>2025/06/28</t>
+  </si>
+  <si>
+    <t>2025/05/24</t>
+  </si>
+  <si>
+    <t>2025/08/02</t>
+  </si>
+  <si>
+    <t>2025/05/03</t>
+  </si>
+  <si>
+    <t>2025/08/09</t>
+  </si>
+  <si>
+    <t>Calford Green</t>
+  </si>
+  <si>
+    <t>58898</t>
+  </si>
+  <si>
+    <t>2025/06/21</t>
+  </si>
+  <si>
+    <t>Bluntisham Recreation Ground</t>
+  </si>
+  <si>
+    <t>13076</t>
+  </si>
+  <si>
+    <t>2025/08/16</t>
+  </si>
+  <si>
+    <t>Histon Recreation Ground</t>
+  </si>
+  <si>
+    <t>10999</t>
+  </si>
+  <si>
+    <t>2025/09/06</t>
+  </si>
+  <si>
+    <t>2025/07/19</t>
+  </si>
+  <si>
+    <t>Thriplow</t>
+  </si>
+  <si>
+    <t>4585</t>
+  </si>
+  <si>
+    <t>Longstanton Recreation Ground</t>
+  </si>
+  <si>
+    <t>12312</t>
   </si>
   <si>
     <t>Abington Cricket Ground</t>
@@ -67,124 +217,10 @@
     <t>13558</t>
   </si>
   <si>
-    <t>2024/07/13</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>Fulbourn Institute CC - 1st XI</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2024/06/15</t>
-  </si>
-  <si>
-    <t>Ramsey CC, Hunts - 2nd XI</t>
-  </si>
-  <si>
-    <t>78071</t>
-  </si>
-  <si>
-    <t>2024/08/17</t>
-  </si>
-  <si>
-    <t>Wilburton CC - 1st XI</t>
-  </si>
-  <si>
-    <t>60408</t>
-  </si>
-  <si>
-    <t>2024/08/03</t>
-  </si>
-  <si>
-    <t>Bluntisham CC - 1st XI</t>
-  </si>
-  <si>
-    <t>41728</t>
-  </si>
-  <si>
-    <t>2024/05/18</t>
-  </si>
-  <si>
-    <t>Horseheath CC - 1st XI</t>
-  </si>
-  <si>
-    <t>134360</t>
-  </si>
-  <si>
-    <t>2024/08/24</t>
-  </si>
-  <si>
-    <t>Wisbech Town CC - 2nd XI</t>
-  </si>
-  <si>
-    <t>14510</t>
-  </si>
-  <si>
-    <t>2024/06/08</t>
-  </si>
-  <si>
-    <t>Longstanton Grasshoppers CC - 1st XI</t>
-  </si>
-  <si>
-    <t>12244</t>
-  </si>
-  <si>
-    <t>2024/05/25</t>
-  </si>
-  <si>
-    <t>City of Ely CC - 1st XI</t>
-  </si>
-  <si>
-    <t>23142</t>
-  </si>
-  <si>
-    <t>2024/07/06</t>
-  </si>
-  <si>
-    <t>The Cricket Meadow, Howards Lane</t>
-  </si>
-  <si>
-    <t>2024/08/31</t>
-  </si>
-  <si>
-    <t>2024/05/04</t>
-  </si>
-  <si>
-    <t>2024/06/22</t>
-  </si>
-  <si>
-    <t>2024/07/27</t>
-  </si>
-  <si>
-    <t>2024/05/11</t>
-  </si>
-  <si>
-    <t>The Piece Ground</t>
-  </si>
-  <si>
-    <t>2191</t>
-  </si>
-  <si>
-    <t>2024/06/01</t>
-  </si>
-  <si>
-    <t>2024/06/29</t>
-  </si>
-  <si>
-    <t>2024/07/20</t>
-  </si>
-  <si>
-    <t>2024/08/10</t>
-  </si>
-  <si>
-    <t>Fulbourn Recreation Ground</t>
-  </si>
-  <si>
-    <t>9770</t>
+    <t>AEH</t>
+  </si>
+  <si>
+    <t>Wendon</t>
   </si>
   <si>
     <t>The Cricketfield</t>
@@ -193,43 +229,61 @@
     <t>14834</t>
   </si>
   <si>
-    <t>Longstanton Recreation Ground</t>
-  </si>
-  <si>
-    <t>12312</t>
-  </si>
-  <si>
-    <t>Thriplow</t>
-  </si>
-  <si>
-    <t>4585</t>
-  </si>
-  <si>
-    <t>Bluntisham Recreation Ground</t>
-  </si>
-  <si>
-    <t>13076</t>
-  </si>
-  <si>
-    <t>Wisbech Town CC</t>
-  </si>
-  <si>
-    <t>11646</t>
-  </si>
-  <si>
-    <t>2024/04/27</t>
-  </si>
-  <si>
-    <t>The Paradise Centre</t>
-  </si>
-  <si>
-    <t>25056</t>
-  </si>
-  <si>
     <t>CCA Junior League 4 South</t>
   </si>
   <si>
-    <t>117812</t>
+    <t>125392</t>
+  </si>
+  <si>
+    <t>Thriplow CC - 3rd XI</t>
+  </si>
+  <si>
+    <t>78712</t>
+  </si>
+  <si>
+    <t>Buntingford CC - 2nd XI</t>
+  </si>
+  <si>
+    <t>134497</t>
+  </si>
+  <si>
+    <t>Fowlmere</t>
+  </si>
+  <si>
+    <t>Elmdon CC - 2nd XI</t>
+  </si>
+  <si>
+    <t>51839</t>
+  </si>
+  <si>
+    <t>Newton CC, Cambs - 1st XI</t>
+  </si>
+  <si>
+    <t>51240</t>
+  </si>
+  <si>
+    <t>Bassingbourn CC - 2nd XI</t>
+  </si>
+  <si>
+    <t>321042</t>
+  </si>
+  <si>
+    <t>Saffron Walden CC - 4th XI</t>
+  </si>
+  <si>
+    <t>68750</t>
+  </si>
+  <si>
+    <t>Linton Village CC - 2nd XI</t>
+  </si>
+  <si>
+    <t>10414</t>
+  </si>
+  <si>
+    <t>Birchanger CC - 2nd XI</t>
+  </si>
+  <si>
+    <t>71201</t>
   </si>
   <si>
     <t>Abington CC, Cambs - 2nd XI</t>
@@ -238,58 +292,31 @@
     <t>29686</t>
   </si>
   <si>
-    <t>Birchanger CC - 2nd XI</t>
-  </si>
-  <si>
-    <t>71201</t>
-  </si>
-  <si>
-    <t>Buntingford CC - 2nd XI</t>
-  </si>
-  <si>
-    <t>134497</t>
-  </si>
-  <si>
-    <t>Cambridge NCI CC - 4th XI</t>
-  </si>
-  <si>
-    <t>56245</t>
-  </si>
-  <si>
-    <t>Newport CC, Essex - 2nd XI</t>
-  </si>
-  <si>
-    <t>48329</t>
-  </si>
-  <si>
-    <t>Linton Village CC - 2nd XI</t>
-  </si>
-  <si>
-    <t>10414</t>
-  </si>
-  <si>
-    <t>Ickleton CC - 2nd XI</t>
-  </si>
-  <si>
-    <t>239150</t>
-  </si>
-  <si>
-    <t>Elmdon CC - 2nd XI</t>
-  </si>
-  <si>
-    <t>51839</t>
-  </si>
-  <si>
-    <t>Newton CC, Cambs - 1st XI</t>
-  </si>
-  <si>
-    <t>51240</t>
-  </si>
-  <si>
-    <t>Birchanger Sports - Social Club</t>
-  </si>
-  <si>
-    <t>Norfolk Rd Playing Field, Bowling Green</t>
+    <t>Bassingbourn Rec</t>
+  </si>
+  <si>
+    <t>8834</t>
+  </si>
+  <si>
+    <t>The Meadow</t>
+  </si>
+  <si>
+    <t>2714</t>
+  </si>
+  <si>
+    <t>Newton CC</t>
+  </si>
+  <si>
+    <t>32992</t>
+  </si>
+  <si>
+    <t>Saffron Walden County High School</t>
+  </si>
+  <si>
+    <t>3112</t>
+  </si>
+  <si>
+    <t>Buntingford</t>
   </si>
   <si>
     <t>Linton Recreation Ground</t>
@@ -298,34 +325,7 @@
     <t>5934</t>
   </si>
   <si>
-    <t>2024/09/07</t>
-  </si>
-  <si>
-    <t>Ickleton Jubilee Oval</t>
-  </si>
-  <si>
-    <t>43879</t>
-  </si>
-  <si>
-    <t>The Meadow</t>
-  </si>
-  <si>
-    <t>2714</t>
-  </si>
-  <si>
-    <t>Frambury Lane, Newport</t>
-  </si>
-  <si>
-    <t>Parkers Piece</t>
-  </si>
-  <si>
-    <t>11904</t>
-  </si>
-  <si>
-    <t>Newton CC</t>
-  </si>
-  <si>
-    <t>32992</t>
+    <t>Birchanger</t>
   </si>
 </sst>
 </file>
@@ -655,7 +655,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="11" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -663,28 +663,31 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
         <v>44</v>
       </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="12" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -692,28 +695,31 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G12" t="s">
         <v>44</v>
       </c>
+      <c r="H12" t="s">
+        <v>45</v>
+      </c>
       <c r="I12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="13" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -721,28 +727,31 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
         <v>44</v>
       </c>
+      <c r="H13" t="s">
+        <v>45</v>
+      </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="14" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -750,28 +759,31 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
         <v>44</v>
       </c>
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
       <c r="I14" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="15" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -779,28 +791,31 @@
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
         <v>44</v>
       </c>
+      <c r="H15" t="s">
+        <v>45</v>
+      </c>
       <c r="I15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="16" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -808,28 +823,31 @@
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
         <v>44</v>
       </c>
+      <c r="H16" t="s">
+        <v>45</v>
+      </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="17" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -837,20 +855,23 @@
         <v>11</v>
       </c>
       <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>33</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" t="s">
-        <v>42</v>
       </c>
       <c r="G17" t="s">
         <v>44</v>
       </c>
+      <c r="H17" t="s">
+        <v>45</v>
+      </c>
       <c r="I17" t="s">
         <v>49</v>
       </c>
@@ -858,7 +879,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="18" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -866,28 +887,31 @@
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
         <v>44</v>
       </c>
+      <c r="H18" t="s">
+        <v>45</v>
+      </c>
       <c r="I18" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="19" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -895,22 +919,25 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
         <v>44</v>
       </c>
+      <c r="H19" t="s">
+        <v>45</v>
+      </c>
       <c r="I19" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -924,25 +951,25 @@
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I20" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
@@ -956,25 +983,25 @@
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H21" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21" t="s">
         <v>51</v>
-      </c>
-      <c r="I21" t="s">
-        <v>53</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -988,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I22" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="J22" t="s">
         <v>19</v>
@@ -1020,25 +1047,25 @@
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I23" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -1052,25 +1079,25 @@
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I24" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -1084,10 +1111,10 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E25" t="s">
         <v>38</v>
@@ -1096,13 +1123,13 @@
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I25" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -1116,25 +1143,25 @@
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J26" t="s">
         <v>19</v>
@@ -1148,25 +1175,25 @@
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E27" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I27" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -1180,25 +1207,25 @@
         <v>11</v>
       </c>
       <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" t="s">
         <v>26</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>27</v>
       </c>
-      <c r="E28" t="s">
-        <v>35</v>
-      </c>
-      <c r="F28" t="s">
-        <v>36</v>
-      </c>
       <c r="G28" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H28" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I28" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="J28" t="s">
         <v>19</v>
@@ -1212,25 +1239,25 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G29" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29" t="s">
         <v>56</v>
       </c>
-      <c r="H29" t="s">
-        <v>57</v>
-      </c>
       <c r="I29" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
@@ -1244,25 +1271,25 @@
         <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F30" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G30" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30" t="s">
         <v>56</v>
       </c>
-      <c r="H30" t="s">
-        <v>57</v>
-      </c>
       <c r="I30" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -1276,10 +1303,10 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
         <v>41</v>
@@ -1288,13 +1315,13 @@
         <v>42</v>
       </c>
       <c r="G31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H31" t="s">
         <v>56</v>
       </c>
-      <c r="H31" t="s">
-        <v>57</v>
-      </c>
       <c r="I31" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
@@ -1308,25 +1335,25 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H32" t="s">
         <v>56</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>57</v>
-      </c>
-      <c r="I32" t="s">
-        <v>37</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
@@ -1340,25 +1367,25 @@
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F33" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G33" t="s">
+        <v>55</v>
+      </c>
+      <c r="H33" t="s">
         <v>56</v>
       </c>
-      <c r="H33" t="s">
-        <v>57</v>
-      </c>
       <c r="I33" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -1372,25 +1399,25 @@
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H34" t="s">
         <v>56</v>
       </c>
-      <c r="H34" t="s">
-        <v>57</v>
-      </c>
       <c r="I34" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
@@ -1404,25 +1431,25 @@
         <v>11</v>
       </c>
       <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" t="s">
         <v>20</v>
       </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
         <v>21</v>
       </c>
-      <c r="E35" t="s">
-        <v>23</v>
-      </c>
-      <c r="F35" t="s">
-        <v>24</v>
-      </c>
       <c r="G35" t="s">
+        <v>55</v>
+      </c>
+      <c r="H35" t="s">
         <v>56</v>
       </c>
-      <c r="H35" t="s">
-        <v>57</v>
-      </c>
       <c r="I35" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -1436,25 +1463,25 @@
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E36" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F36" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G36" t="s">
+        <v>55</v>
+      </c>
+      <c r="H36" t="s">
         <v>56</v>
       </c>
-      <c r="H36" t="s">
-        <v>57</v>
-      </c>
       <c r="I36" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J36" t="s">
         <v>19</v>
@@ -1468,25 +1495,25 @@
         <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H37" t="s">
         <v>56</v>
       </c>
-      <c r="H37" t="s">
-        <v>57</v>
-      </c>
       <c r="I37" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
@@ -1500,16 +1527,16 @@
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F38" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G38" t="s">
         <v>58</v>
@@ -1518,7 +1545,7 @@
         <v>59</v>
       </c>
       <c r="I38" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="J38" t="s">
         <v>19</v>
@@ -1532,16 +1559,16 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F39" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G39" t="s">
         <v>58</v>
@@ -1564,10 +1591,10 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E40" t="s">
         <v>20</v>
@@ -1582,7 +1609,7 @@
         <v>59</v>
       </c>
       <c r="I40" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="J40" t="s">
         <v>19</v>
@@ -1596,16 +1623,16 @@
         <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D41" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G41" t="s">
         <v>58</v>
@@ -1614,7 +1641,7 @@
         <v>59</v>
       </c>
       <c r="I41" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
@@ -1628,16 +1655,16 @@
         <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D42" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E42" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F42" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
         <v>58</v>
@@ -1646,7 +1673,7 @@
         <v>59</v>
       </c>
       <c r="I42" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
@@ -1660,16 +1687,16 @@
         <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E43" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G43" t="s">
         <v>58</v>
@@ -1678,7 +1705,7 @@
         <v>59</v>
       </c>
       <c r="I43" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
@@ -1692,10 +1719,10 @@
         <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E44" t="s">
         <v>26</v>
@@ -1710,7 +1737,7 @@
         <v>59</v>
       </c>
       <c r="I44" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
@@ -1724,16 +1751,16 @@
         <v>11</v>
       </c>
       <c r="C45" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" t="s">
         <v>23</v>
       </c>
-      <c r="D45" t="s">
+      <c r="F45" t="s">
         <v>24</v>
-      </c>
-      <c r="E45" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" t="s">
-        <v>15</v>
       </c>
       <c r="G45" t="s">
         <v>58</v>
@@ -1742,7 +1769,7 @@
         <v>59</v>
       </c>
       <c r="I45" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
@@ -1756,16 +1783,16 @@
         <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E46" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F46" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G46" t="s">
         <v>58</v>
@@ -1774,7 +1801,7 @@
         <v>59</v>
       </c>
       <c r="I46" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J46" t="s">
         <v>19</v>
@@ -1788,25 +1815,25 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G47" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H47" t="s">
+        <v>63</v>
+      </c>
+      <c r="I47" t="s">
         <v>61</v>
-      </c>
-      <c r="I47" t="s">
-        <v>55</v>
       </c>
       <c r="J47" t="s">
         <v>19</v>
@@ -1820,25 +1847,25 @@
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D48" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E48" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F48" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G48" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H48" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
@@ -1852,25 +1879,25 @@
         <v>11</v>
       </c>
       <c r="C49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" t="s">
         <v>38</v>
       </c>
-      <c r="D49" t="s">
+      <c r="F49" t="s">
         <v>39</v>
       </c>
-      <c r="E49" t="s">
-        <v>29</v>
-      </c>
-      <c r="F49" t="s">
-        <v>30</v>
-      </c>
       <c r="G49" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H49" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I49" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J49" t="s">
         <v>19</v>
@@ -1884,10 +1911,10 @@
         <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E50" t="s">
         <v>35</v>
@@ -1896,13 +1923,13 @@
         <v>36</v>
       </c>
       <c r="G50" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H50" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I50" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J50" t="s">
         <v>19</v>
@@ -1916,25 +1943,25 @@
         <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E51" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G51" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H51" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J51" t="s">
         <v>19</v>
@@ -1948,25 +1975,25 @@
         <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D52" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E52" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H52" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I52" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J52" t="s">
         <v>19</v>
@@ -1980,25 +2007,25 @@
         <v>11</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E53" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F53" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H53" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I53" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="J53" t="s">
         <v>19</v>
@@ -2012,25 +2039,25 @@
         <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D54" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E54" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F54" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G54" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H54" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I54" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J54" t="s">
         <v>19</v>
@@ -2044,25 +2071,25 @@
         <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E55" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G55" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H55" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I55" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J55" t="s">
         <v>19</v>
@@ -2076,25 +2103,25 @@
         <v>11</v>
       </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F56" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G56" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H56" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I56" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J56" t="s">
         <v>19</v>
@@ -2108,10 +2135,10 @@
         <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D57" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E57" t="s">
         <v>32</v>
@@ -2120,13 +2147,13 @@
         <v>33</v>
       </c>
       <c r="G57" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H57" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I57" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J57" t="s">
         <v>19</v>
@@ -2140,25 +2167,25 @@
         <v>11</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D58" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E58" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F58" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G58" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H58" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I58" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J58" t="s">
         <v>19</v>
@@ -2172,22 +2199,22 @@
         <v>11</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D59" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E59" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F59" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G59" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H59" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I59" t="s">
         <v>22</v>
@@ -2204,25 +2231,25 @@
         <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D60" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E60" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G60" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H60" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I60" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J60" t="s">
         <v>19</v>
@@ -2236,25 +2263,25 @@
         <v>11</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E61" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G61" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H61" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I61" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J61" t="s">
         <v>19</v>
@@ -2268,25 +2295,25 @@
         <v>11</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E62" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H62" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I62" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J62" t="s">
         <v>19</v>
@@ -2300,25 +2327,25 @@
         <v>11</v>
       </c>
       <c r="C63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D63" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" t="s">
         <v>14</v>
       </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
         <v>15</v>
       </c>
-      <c r="E63" t="s">
-        <v>20</v>
-      </c>
-      <c r="F63" t="s">
-        <v>21</v>
-      </c>
       <c r="G63" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H63" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I63" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J63" t="s">
         <v>19</v>
@@ -2332,25 +2359,25 @@
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D64" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E64" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F64" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I64" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="J64" t="s">
         <v>19</v>
@@ -2364,10 +2391,10 @@
         <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D65" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E65" t="s">
         <v>14</v>
@@ -2376,13 +2403,13 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H65" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I65" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J65" t="s">
         <v>19</v>
@@ -2396,25 +2423,25 @@
         <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D66" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E66" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="F66" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I66" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="J66" t="s">
         <v>19</v>
@@ -2428,25 +2455,25 @@
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D67" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E67" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F67" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G67" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H67" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I67" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J67" t="s">
         <v>19</v>
@@ -2460,25 +2487,25 @@
         <v>11</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D68" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E68" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F68" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G68" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H68" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I68" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J68" t="s">
         <v>19</v>
@@ -2492,25 +2519,25 @@
         <v>11</v>
       </c>
       <c r="C69" t="s">
+        <v>38</v>
+      </c>
+      <c r="D69" t="s">
+        <v>39</v>
+      </c>
+      <c r="E69" t="s">
         <v>29</v>
       </c>
-      <c r="D69" t="s">
+      <c r="F69" t="s">
         <v>30</v>
       </c>
-      <c r="E69" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69" t="s">
-        <v>13</v>
-      </c>
       <c r="G69" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H69" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I69" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J69" t="s">
         <v>19</v>
@@ -2524,25 +2551,25 @@
         <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D70" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E70" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F70" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G70" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H70" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I70" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="J70" t="s">
         <v>19</v>
@@ -2556,25 +2583,25 @@
         <v>11</v>
       </c>
       <c r="C71" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D71" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E71" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F71" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G71" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H71" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I71" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="J71" t="s">
         <v>19</v>
@@ -2588,25 +2615,25 @@
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D72" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E72" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G72" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H72" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I72" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="J72" t="s">
         <v>19</v>
@@ -2620,313 +2647,286 @@
         <v>11</v>
       </c>
       <c r="C73" t="s">
+        <v>38</v>
+      </c>
+      <c r="D73" t="s">
+        <v>39</v>
+      </c>
+      <c r="E73" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" t="s">
+        <v>33</v>
+      </c>
+      <c r="G73" t="s">
+        <v>66</v>
+      </c>
+      <c r="H73" t="s">
+        <v>67</v>
+      </c>
+      <c r="I73" t="s">
+        <v>25</v>
+      </c>
+      <c r="J73" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A74" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74" t="s">
+        <v>24</v>
+      </c>
+      <c r="G74" t="s">
+        <v>68</v>
+      </c>
+      <c r="I74" t="s">
+        <v>46</v>
+      </c>
+      <c r="J74" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A75" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" t="s">
         <v>29</v>
       </c>
-      <c r="D73" t="s">
+      <c r="F75" t="s">
         <v>30</v>
       </c>
-      <c r="E73" t="s">
+      <c r="G75" t="s">
+        <v>68</v>
+      </c>
+      <c r="I75" t="s">
+        <v>43</v>
+      </c>
+      <c r="J75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A76" t="s">
+        <v>10</v>
+      </c>
+      <c r="B76" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" t="s">
+        <v>26</v>
+      </c>
+      <c r="F76" t="s">
+        <v>27</v>
+      </c>
+      <c r="G76" t="s">
+        <v>68</v>
+      </c>
+      <c r="I76" t="s">
+        <v>22</v>
+      </c>
+      <c r="J76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A77" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" t="s">
+        <v>68</v>
+      </c>
+      <c r="I77" t="s">
+        <v>61</v>
+      </c>
+      <c r="J77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A78" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" t="s">
+        <v>32</v>
+      </c>
+      <c r="F78" t="s">
+        <v>33</v>
+      </c>
+      <c r="G78" t="s">
+        <v>69</v>
+      </c>
+      <c r="I78" t="s">
+        <v>60</v>
+      </c>
+      <c r="J78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A79" t="s">
+        <v>10</v>
+      </c>
+      <c r="B79" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" t="s">
         <v>20</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F79" t="s">
         <v>21</v>
       </c>
-      <c r="G73" t="s">
-        <v>64</v>
-      </c>
-      <c r="H73" t="s">
-        <v>65</v>
-      </c>
-      <c r="I73" t="s">
-        <v>46</v>
-      </c>
-      <c r="J73" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="74" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A74" t="s">
-        <v>10</v>
-      </c>
-      <c r="B74" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="G79" t="s">
+        <v>68</v>
+      </c>
+      <c r="I79" t="s">
+        <v>54</v>
+      </c>
+      <c r="J79" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A80" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" t="s">
+        <v>15</v>
+      </c>
+      <c r="E80" t="s">
+        <v>41</v>
+      </c>
+      <c r="F80" t="s">
+        <v>42</v>
+      </c>
+      <c r="G80" t="s">
+        <v>68</v>
+      </c>
+      <c r="I80" t="s">
+        <v>34</v>
+      </c>
+      <c r="J80" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A81" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" t="s">
+        <v>39</v>
+      </c>
+      <c r="G81" t="s">
+        <v>68</v>
+      </c>
+      <c r="I81" t="s">
+        <v>37</v>
+      </c>
+      <c r="J81" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" t="s">
+        <v>14</v>
+      </c>
+      <c r="D82" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" t="s">
         <v>35</v>
       </c>
-      <c r="D74" t="s">
+      <c r="F82" t="s">
         <v>36</v>
       </c>
-      <c r="E74" t="s">
-        <v>26</v>
-      </c>
-      <c r="F74" t="s">
-        <v>27</v>
-      </c>
-      <c r="G74" t="s">
-        <v>66</v>
-      </c>
-      <c r="H74" t="s">
-        <v>67</v>
-      </c>
-      <c r="I74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J74" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="75" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A75" t="s">
-        <v>10</v>
-      </c>
-      <c r="B75" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" t="s">
-        <v>35</v>
-      </c>
-      <c r="D75" t="s">
-        <v>36</v>
-      </c>
-      <c r="E75" t="s">
-        <v>38</v>
-      </c>
-      <c r="F75" t="s">
-        <v>39</v>
-      </c>
-      <c r="G75" t="s">
-        <v>66</v>
-      </c>
-      <c r="H75" t="s">
-        <v>67</v>
-      </c>
-      <c r="I75" t="s">
-        <v>54</v>
-      </c>
-      <c r="J75" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="76" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A76" t="s">
-        <v>10</v>
-      </c>
-      <c r="B76" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" t="s">
-        <v>35</v>
-      </c>
-      <c r="D76" t="s">
-        <v>36</v>
-      </c>
-      <c r="E76" t="s">
-        <v>23</v>
-      </c>
-      <c r="F76" t="s">
-        <v>24</v>
-      </c>
-      <c r="G76" t="s">
-        <v>66</v>
-      </c>
-      <c r="H76" t="s">
-        <v>67</v>
-      </c>
-      <c r="I76" t="s">
+      <c r="G82" t="s">
         <v>68</v>
       </c>
-      <c r="J76" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="77" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A77" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" t="s">
-        <v>35</v>
-      </c>
-      <c r="D77" t="s">
-        <v>36</v>
-      </c>
-      <c r="E77" t="s">
-        <v>41</v>
-      </c>
-      <c r="F77" t="s">
-        <v>42</v>
-      </c>
-      <c r="G77" t="s">
-        <v>66</v>
-      </c>
-      <c r="H77" t="s">
-        <v>67</v>
-      </c>
-      <c r="I77" t="s">
-        <v>52</v>
-      </c>
-      <c r="J77" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="78" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A78" t="s">
-        <v>10</v>
-      </c>
-      <c r="B78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" t="s">
-        <v>35</v>
-      </c>
-      <c r="D78" t="s">
-        <v>36</v>
-      </c>
-      <c r="E78" t="s">
-        <v>20</v>
-      </c>
-      <c r="F78" t="s">
-        <v>21</v>
-      </c>
-      <c r="G78" t="s">
-        <v>66</v>
-      </c>
-      <c r="H78" t="s">
-        <v>67</v>
-      </c>
-      <c r="I78" t="s">
-        <v>28</v>
-      </c>
-      <c r="J78" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="79" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A79" t="s">
-        <v>10</v>
-      </c>
-      <c r="B79" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" t="s">
-        <v>35</v>
-      </c>
-      <c r="D79" t="s">
-        <v>36</v>
-      </c>
-      <c r="E79" t="s">
-        <v>32</v>
-      </c>
-      <c r="F79" t="s">
-        <v>33</v>
-      </c>
-      <c r="G79" t="s">
-        <v>66</v>
-      </c>
-      <c r="H79" t="s">
-        <v>67</v>
-      </c>
-      <c r="I79" t="s">
-        <v>55</v>
-      </c>
-      <c r="J79" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="80" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A80" t="s">
-        <v>10</v>
-      </c>
-      <c r="B80" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" t="s">
-        <v>35</v>
-      </c>
-      <c r="D80" t="s">
-        <v>36</v>
-      </c>
-      <c r="E80" t="s">
-        <v>29</v>
-      </c>
-      <c r="F80" t="s">
-        <v>30</v>
-      </c>
-      <c r="G80" t="s">
-        <v>66</v>
-      </c>
-      <c r="H80" t="s">
-        <v>67</v>
-      </c>
-      <c r="I80" t="s">
-        <v>43</v>
-      </c>
-      <c r="J80" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="81" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A81" t="s">
-        <v>10</v>
-      </c>
-      <c r="B81" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81" t="s">
-        <v>35</v>
-      </c>
-      <c r="D81" t="s">
-        <v>36</v>
-      </c>
-      <c r="E81" t="s">
-        <v>14</v>
-      </c>
-      <c r="F81" t="s">
-        <v>15</v>
-      </c>
-      <c r="G81" t="s">
-        <v>66</v>
-      </c>
-      <c r="H81" t="s">
-        <v>67</v>
-      </c>
-      <c r="I81" t="s">
-        <v>34</v>
-      </c>
-      <c r="J81" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="82" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A82" t="s">
-        <v>10</v>
-      </c>
-      <c r="B82" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" t="s">
-        <v>35</v>
-      </c>
-      <c r="D82" t="s">
-        <v>36</v>
-      </c>
-      <c r="E82" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" t="s">
-        <v>13</v>
-      </c>
-      <c r="G82" t="s">
-        <v>66</v>
-      </c>
-      <c r="H82" t="s">
-        <v>67</v>
-      </c>
       <c r="I82" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J82" t="s">
         <v>19</v>
@@ -2940,25 +2940,25 @@
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D83" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E83" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F83" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G83" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I83" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J83" t="s">
         <v>19</v>
@@ -2972,25 +2972,25 @@
         <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D84" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E84" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G84" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I84" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J84" t="s">
         <v>19</v>
@@ -3004,25 +3004,25 @@
         <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D85" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E85" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F85" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G85" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I85" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J85" t="s">
         <v>19</v>
@@ -3036,25 +3036,25 @@
         <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D86" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E86" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F86" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G86" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I86" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="J86" t="s">
         <v>19</v>
@@ -3068,25 +3068,25 @@
         <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D87" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E87" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F87" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G87" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H87" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I87" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J87" t="s">
         <v>19</v>
@@ -3100,10 +3100,10 @@
         <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D88" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E88" t="s">
         <v>14</v>
@@ -3112,13 +3112,13 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I88" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J88" t="s">
         <v>19</v>
@@ -3132,25 +3132,25 @@
         <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D89" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E89" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F89" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G89" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H89" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I89" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J89" t="s">
         <v>19</v>
@@ -3164,25 +3164,25 @@
         <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D90" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E90" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F90" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G90" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I90" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="J90" t="s">
         <v>19</v>
@@ -3196,307 +3196,286 @@
         <v>11</v>
       </c>
       <c r="C91" t="s">
+        <v>35</v>
+      </c>
+      <c r="D91" t="s">
+        <v>36</v>
+      </c>
+      <c r="E91" t="s">
         <v>41</v>
       </c>
-      <c r="D91" t="s">
+      <c r="F91" t="s">
         <v>42</v>
       </c>
-      <c r="E91" t="s">
-        <v>12</v>
-      </c>
-      <c r="F91" t="s">
-        <v>13</v>
-      </c>
       <c r="G91" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I91" t="s">
+        <v>28</v>
+      </c>
+      <c r="J91" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A92" t="s">
+        <v>72</v>
+      </c>
+      <c r="B92" t="s">
+        <v>73</v>
+      </c>
+      <c r="C92" t="s">
+        <v>74</v>
+      </c>
+      <c r="D92" t="s">
+        <v>75</v>
+      </c>
+      <c r="E92" t="s">
+        <v>76</v>
+      </c>
+      <c r="F92" t="s">
+        <v>77</v>
+      </c>
+      <c r="G92" t="s">
+        <v>78</v>
+      </c>
+      <c r="I92" t="s">
         <v>48</v>
       </c>
-      <c r="J91" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="92" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A92" t="s">
-        <v>71</v>
-      </c>
-      <c r="B92" t="s">
-        <v>72</v>
-      </c>
-      <c r="C92" t="s">
-        <v>73</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="J92" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A93" t="s">
+        <v>72</v>
+      </c>
+      <c r="B93" t="s">
+        <v>73</v>
+      </c>
+      <c r="C93" t="s">
         <v>74</v>
       </c>
-      <c r="E92" t="s">
+      <c r="D93" t="s">
         <v>75</v>
       </c>
-      <c r="F92" t="s">
-        <v>76</v>
-      </c>
-      <c r="G92" t="s">
-        <v>16</v>
-      </c>
-      <c r="H92" t="s">
-        <v>17</v>
-      </c>
-      <c r="I92" t="s">
-        <v>52</v>
-      </c>
-      <c r="J92" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="93" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A93" t="s">
-        <v>71</v>
-      </c>
-      <c r="B93" t="s">
-        <v>72</v>
-      </c>
-      <c r="C93" t="s">
-        <v>73</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
+        <v>79</v>
+      </c>
+      <c r="F93" t="s">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s">
+        <v>78</v>
+      </c>
+      <c r="I93" t="s">
+        <v>25</v>
+      </c>
+      <c r="J93" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A94" t="s">
+        <v>72</v>
+      </c>
+      <c r="B94" t="s">
+        <v>73</v>
+      </c>
+      <c r="C94" t="s">
         <v>74</v>
       </c>
-      <c r="E93" t="s">
-        <v>77</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="D94" t="s">
+        <v>75</v>
+      </c>
+      <c r="E94" t="s">
+        <v>81</v>
+      </c>
+      <c r="F94" t="s">
+        <v>82</v>
+      </c>
+      <c r="G94" t="s">
         <v>78</v>
       </c>
-      <c r="G93" t="s">
-        <v>16</v>
-      </c>
-      <c r="H93" t="s">
-        <v>17</v>
-      </c>
-      <c r="I93" t="s">
-        <v>55</v>
-      </c>
-      <c r="J93" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="94" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A94" t="s">
-        <v>71</v>
-      </c>
-      <c r="B94" t="s">
-        <v>72</v>
-      </c>
-      <c r="C94" t="s">
-        <v>73</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="I94" t="s">
+        <v>43</v>
+      </c>
+      <c r="J94" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A95" t="s">
+        <v>72</v>
+      </c>
+      <c r="B95" t="s">
+        <v>73</v>
+      </c>
+      <c r="C95" t="s">
         <v>74</v>
       </c>
-      <c r="E94" t="s">
-        <v>79</v>
-      </c>
-      <c r="F94" t="s">
-        <v>80</v>
-      </c>
-      <c r="G94" t="s">
-        <v>16</v>
-      </c>
-      <c r="H94" t="s">
-        <v>17</v>
-      </c>
-      <c r="I94" t="s">
-        <v>53</v>
-      </c>
-      <c r="J94" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="95" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A95" t="s">
-        <v>71</v>
-      </c>
-      <c r="B95" t="s">
-        <v>72</v>
-      </c>
-      <c r="C95" t="s">
-        <v>73</v>
-      </c>
       <c r="D95" t="s">
+        <v>75</v>
+      </c>
+      <c r="E95" t="s">
+        <v>83</v>
+      </c>
+      <c r="F95" t="s">
+        <v>84</v>
+      </c>
+      <c r="G95" t="s">
+        <v>78</v>
+      </c>
+      <c r="I95" t="s">
+        <v>40</v>
+      </c>
+      <c r="J95" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A96" t="s">
+        <v>72</v>
+      </c>
+      <c r="B96" t="s">
+        <v>73</v>
+      </c>
+      <c r="C96" t="s">
         <v>74</v>
       </c>
-      <c r="E95" t="s">
-        <v>81</v>
-      </c>
-      <c r="F95" t="s">
-        <v>82</v>
-      </c>
-      <c r="G95" t="s">
-        <v>16</v>
-      </c>
-      <c r="H95" t="s">
-        <v>17</v>
-      </c>
-      <c r="I95" t="s">
-        <v>48</v>
-      </c>
-      <c r="J95" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="96" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A96" t="s">
-        <v>71</v>
-      </c>
-      <c r="B96" t="s">
-        <v>72</v>
-      </c>
-      <c r="C96" t="s">
-        <v>73</v>
-      </c>
       <c r="D96" t="s">
+        <v>75</v>
+      </c>
+      <c r="E96" t="s">
+        <v>85</v>
+      </c>
+      <c r="F96" t="s">
+        <v>86</v>
+      </c>
+      <c r="G96" t="s">
+        <v>78</v>
+      </c>
+      <c r="I96" t="s">
+        <v>50</v>
+      </c>
+      <c r="J96" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A97" t="s">
+        <v>72</v>
+      </c>
+      <c r="B97" t="s">
+        <v>73</v>
+      </c>
+      <c r="C97" t="s">
         <v>74</v>
       </c>
-      <c r="E96" t="s">
+      <c r="D97" t="s">
+        <v>75</v>
+      </c>
+      <c r="E97" t="s">
+        <v>87</v>
+      </c>
+      <c r="F97" t="s">
+        <v>88</v>
+      </c>
+      <c r="G97" t="s">
+        <v>78</v>
+      </c>
+      <c r="I97" t="s">
+        <v>37</v>
+      </c>
+      <c r="J97" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A98" t="s">
+        <v>72</v>
+      </c>
+      <c r="B98" t="s">
+        <v>73</v>
+      </c>
+      <c r="C98" t="s">
+        <v>74</v>
+      </c>
+      <c r="D98" t="s">
+        <v>75</v>
+      </c>
+      <c r="E98" t="s">
+        <v>89</v>
+      </c>
+      <c r="F98" t="s">
+        <v>90</v>
+      </c>
+      <c r="G98" t="s">
+        <v>78</v>
+      </c>
+      <c r="I98" t="s">
+        <v>47</v>
+      </c>
+      <c r="J98" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" x14ac:dyDescent="0.25" spans="1:9">
+      <c r="A99" t="s">
+        <v>72</v>
+      </c>
+      <c r="B99" t="s">
+        <v>73</v>
+      </c>
+      <c r="C99" t="s">
+        <v>74</v>
+      </c>
+      <c r="D99" t="s">
+        <v>75</v>
+      </c>
+      <c r="E99" t="s">
+        <v>91</v>
+      </c>
+      <c r="F99" t="s">
+        <v>92</v>
+      </c>
+      <c r="G99" t="s">
+        <v>78</v>
+      </c>
+      <c r="I99" t="s">
+        <v>49</v>
+      </c>
+      <c r="J99" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A100" t="s">
+        <v>72</v>
+      </c>
+      <c r="B100" t="s">
+        <v>73</v>
+      </c>
+      <c r="C100" t="s">
         <v>83</v>
       </c>
-      <c r="F96" t="s">
+      <c r="D100" t="s">
         <v>84</v>
       </c>
-      <c r="G96" t="s">
-        <v>16</v>
-      </c>
-      <c r="H96" t="s">
-        <v>17</v>
-      </c>
-      <c r="I96" t="s">
-        <v>45</v>
-      </c>
-      <c r="J96" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="97" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A97" t="s">
-        <v>71</v>
-      </c>
-      <c r="B97" t="s">
-        <v>72</v>
-      </c>
-      <c r="C97" t="s">
-        <v>73</v>
-      </c>
-      <c r="D97" t="s">
-        <v>74</v>
-      </c>
-      <c r="E97" t="s">
-        <v>85</v>
-      </c>
-      <c r="F97" t="s">
-        <v>86</v>
-      </c>
-      <c r="G97" t="s">
-        <v>16</v>
-      </c>
-      <c r="H97" t="s">
-        <v>17</v>
-      </c>
-      <c r="I97" t="s">
-        <v>49</v>
-      </c>
-      <c r="J97" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="98" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A98" t="s">
-        <v>71</v>
-      </c>
-      <c r="B98" t="s">
-        <v>72</v>
-      </c>
-      <c r="C98" t="s">
-        <v>73</v>
-      </c>
-      <c r="D98" t="s">
-        <v>74</v>
-      </c>
-      <c r="E98" t="s">
-        <v>87</v>
-      </c>
-      <c r="F98" t="s">
-        <v>88</v>
-      </c>
-      <c r="G98" t="s">
-        <v>16</v>
-      </c>
-      <c r="H98" t="s">
-        <v>17</v>
-      </c>
-      <c r="I98" t="s">
-        <v>46</v>
-      </c>
-      <c r="J98" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="99" x14ac:dyDescent="0.25" spans="1:10">
-      <c r="A99" t="s">
-        <v>71</v>
-      </c>
-      <c r="B99" t="s">
-        <v>72</v>
-      </c>
-      <c r="C99" t="s">
-        <v>73</v>
-      </c>
-      <c r="D99" t="s">
-        <v>74</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="E100" t="s">
         <v>89</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F100" t="s">
         <v>90</v>
       </c>
-      <c r="G99" t="s">
-        <v>16</v>
-      </c>
-      <c r="H99" t="s">
-        <v>17</v>
-      </c>
-      <c r="I99" t="s">
-        <v>54</v>
-      </c>
-      <c r="J99" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="100" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A100" t="s">
-        <v>71</v>
-      </c>
-      <c r="B100" t="s">
-        <v>72</v>
-      </c>
-      <c r="C100" t="s">
-        <v>75</v>
-      </c>
-      <c r="D100" t="s">
-        <v>76</v>
-      </c>
-      <c r="E100" t="s">
-        <v>79</v>
-      </c>
-      <c r="F100" t="s">
-        <v>80</v>
-      </c>
       <c r="G100" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="H100" t="s">
+        <v>94</v>
       </c>
       <c r="I100" t="s">
         <v>34</v>
@@ -3505,27 +3484,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="101" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C101" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D101" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E101" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F101" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G101" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="H101" t="s">
+        <v>94</v>
       </c>
       <c r="I101" t="s">
         <v>49</v>
@@ -3534,308 +3516,338 @@
         <v>19</v>
       </c>
     </row>
-    <row r="102" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="102" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A102" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B102" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C102" t="s">
+        <v>83</v>
+      </c>
+      <c r="D102" t="s">
+        <v>84</v>
+      </c>
+      <c r="E102" t="s">
+        <v>87</v>
+      </c>
+      <c r="F102" t="s">
+        <v>88</v>
+      </c>
+      <c r="G102" t="s">
+        <v>93</v>
+      </c>
+      <c r="H102" t="s">
+        <v>94</v>
+      </c>
+      <c r="I102" t="s">
+        <v>50</v>
+      </c>
+      <c r="J102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A103" t="s">
+        <v>72</v>
+      </c>
+      <c r="B103" t="s">
+        <v>73</v>
+      </c>
+      <c r="C103" t="s">
+        <v>83</v>
+      </c>
+      <c r="D103" t="s">
+        <v>84</v>
+      </c>
+      <c r="E103" t="s">
+        <v>91</v>
+      </c>
+      <c r="F103" t="s">
+        <v>92</v>
+      </c>
+      <c r="G103" t="s">
+        <v>93</v>
+      </c>
+      <c r="H103" t="s">
+        <v>94</v>
+      </c>
+      <c r="I103" t="s">
+        <v>46</v>
+      </c>
+      <c r="J103" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A104" t="s">
+        <v>72</v>
+      </c>
+      <c r="B104" t="s">
+        <v>73</v>
+      </c>
+      <c r="C104" t="s">
+        <v>83</v>
+      </c>
+      <c r="D104" t="s">
+        <v>84</v>
+      </c>
+      <c r="E104" t="s">
+        <v>81</v>
+      </c>
+      <c r="F104" t="s">
+        <v>82</v>
+      </c>
+      <c r="G104" t="s">
+        <v>93</v>
+      </c>
+      <c r="H104" t="s">
+        <v>94</v>
+      </c>
+      <c r="I104" t="s">
+        <v>18</v>
+      </c>
+      <c r="J104" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A105" t="s">
+        <v>72</v>
+      </c>
+      <c r="B105" t="s">
+        <v>73</v>
+      </c>
+      <c r="C105" t="s">
+        <v>83</v>
+      </c>
+      <c r="D105" t="s">
+        <v>84</v>
+      </c>
+      <c r="E105" t="s">
+        <v>74</v>
+      </c>
+      <c r="F105" t="s">
         <v>75</v>
       </c>
-      <c r="D102" t="s">
+      <c r="G105" t="s">
+        <v>93</v>
+      </c>
+      <c r="H105" t="s">
+        <v>94</v>
+      </c>
+      <c r="I105" t="s">
+        <v>54</v>
+      </c>
+      <c r="J105" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A106" t="s">
+        <v>72</v>
+      </c>
+      <c r="B106" t="s">
+        <v>73</v>
+      </c>
+      <c r="C106" t="s">
+        <v>83</v>
+      </c>
+      <c r="D106" t="s">
+        <v>84</v>
+      </c>
+      <c r="E106" t="s">
         <v>76</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F106" t="s">
+        <v>77</v>
+      </c>
+      <c r="G106" t="s">
+        <v>93</v>
+      </c>
+      <c r="H106" t="s">
+        <v>94</v>
+      </c>
+      <c r="I106" t="s">
+        <v>51</v>
+      </c>
+      <c r="J106" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A107" t="s">
+        <v>72</v>
+      </c>
+      <c r="B107" t="s">
+        <v>73</v>
+      </c>
+      <c r="C107" t="s">
+        <v>83</v>
+      </c>
+      <c r="D107" t="s">
+        <v>84</v>
+      </c>
+      <c r="E107" t="s">
+        <v>85</v>
+      </c>
+      <c r="F107" t="s">
+        <v>86</v>
+      </c>
+      <c r="G107" t="s">
+        <v>93</v>
+      </c>
+      <c r="H107" t="s">
+        <v>94</v>
+      </c>
+      <c r="I107" t="s">
+        <v>31</v>
+      </c>
+      <c r="J107" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A108" t="s">
+        <v>72</v>
+      </c>
+      <c r="B108" t="s">
+        <v>73</v>
+      </c>
+      <c r="C108" t="s">
+        <v>91</v>
+      </c>
+      <c r="D108" t="s">
+        <v>92</v>
+      </c>
+      <c r="E108" t="s">
+        <v>76</v>
+      </c>
+      <c r="F108" t="s">
+        <v>77</v>
+      </c>
+      <c r="G108" t="s">
+        <v>66</v>
+      </c>
+      <c r="H108" t="s">
+        <v>67</v>
+      </c>
+      <c r="I108" t="s">
+        <v>18</v>
+      </c>
+      <c r="J108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A109" t="s">
+        <v>72</v>
+      </c>
+      <c r="B109" t="s">
+        <v>73</v>
+      </c>
+      <c r="C109" t="s">
+        <v>91</v>
+      </c>
+      <c r="D109" t="s">
+        <v>92</v>
+      </c>
+      <c r="E109" t="s">
+        <v>87</v>
+      </c>
+      <c r="F109" t="s">
+        <v>88</v>
+      </c>
+      <c r="G109" t="s">
+        <v>66</v>
+      </c>
+      <c r="H109" t="s">
+        <v>67</v>
+      </c>
+      <c r="I109" t="s">
+        <v>40</v>
+      </c>
+      <c r="J109" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A110" t="s">
+        <v>72</v>
+      </c>
+      <c r="B110" t="s">
+        <v>73</v>
+      </c>
+      <c r="C110" t="s">
+        <v>91</v>
+      </c>
+      <c r="D110" t="s">
+        <v>92</v>
+      </c>
+      <c r="E110" t="s">
+        <v>81</v>
+      </c>
+      <c r="F110" t="s">
+        <v>82</v>
+      </c>
+      <c r="G110" t="s">
+        <v>66</v>
+      </c>
+      <c r="H110" t="s">
+        <v>67</v>
+      </c>
+      <c r="I110" t="s">
+        <v>22</v>
+      </c>
+      <c r="J110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A111" t="s">
+        <v>72</v>
+      </c>
+      <c r="B111" t="s">
+        <v>73</v>
+      </c>
+      <c r="C111" t="s">
+        <v>91</v>
+      </c>
+      <c r="D111" t="s">
+        <v>92</v>
+      </c>
+      <c r="E111" t="s">
         <v>89</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F111" t="s">
         <v>90</v>
       </c>
-      <c r="G102" t="s">
+      <c r="G111" t="s">
+        <v>66</v>
+      </c>
+      <c r="H111" t="s">
+        <v>67</v>
+      </c>
+      <c r="I111" t="s">
+        <v>37</v>
+      </c>
+      <c r="J111" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A112" t="s">
+        <v>72</v>
+      </c>
+      <c r="B112" t="s">
+        <v>73</v>
+      </c>
+      <c r="C112" t="s">
         <v>91</v>
       </c>
-      <c r="I102" t="s">
-        <v>22</v>
-      </c>
-      <c r="J102" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="103" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A103" t="s">
-        <v>71</v>
-      </c>
-      <c r="B103" t="s">
-        <v>72</v>
-      </c>
-      <c r="C103" t="s">
-        <v>75</v>
-      </c>
-      <c r="D103" t="s">
-        <v>76</v>
-      </c>
-      <c r="E103" t="s">
-        <v>85</v>
-      </c>
-      <c r="F103" t="s">
-        <v>86</v>
-      </c>
-      <c r="G103" t="s">
-        <v>91</v>
-      </c>
-      <c r="I103" t="s">
-        <v>45</v>
-      </c>
-      <c r="J103" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="104" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A104" t="s">
-        <v>71</v>
-      </c>
-      <c r="B104" t="s">
-        <v>72</v>
-      </c>
-      <c r="C104" t="s">
-        <v>75</v>
-      </c>
-      <c r="D104" t="s">
-        <v>76</v>
-      </c>
-      <c r="E104" t="s">
-        <v>77</v>
-      </c>
-      <c r="F104" t="s">
-        <v>78</v>
-      </c>
-      <c r="G104" t="s">
-        <v>91</v>
-      </c>
-      <c r="I104" t="s">
-        <v>40</v>
-      </c>
-      <c r="J104" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="105" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A105" t="s">
-        <v>71</v>
-      </c>
-      <c r="B105" t="s">
-        <v>72</v>
-      </c>
-      <c r="C105" t="s">
-        <v>75</v>
-      </c>
-      <c r="D105" t="s">
-        <v>76</v>
-      </c>
-      <c r="E105" t="s">
-        <v>81</v>
-      </c>
-      <c r="F105" t="s">
-        <v>82</v>
-      </c>
-      <c r="G105" t="s">
-        <v>91</v>
-      </c>
-      <c r="I105" t="s">
-        <v>46</v>
-      </c>
-      <c r="J105" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="106" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A106" t="s">
-        <v>71</v>
-      </c>
-      <c r="B106" t="s">
-        <v>72</v>
-      </c>
-      <c r="C106" t="s">
-        <v>75</v>
-      </c>
-      <c r="D106" t="s">
-        <v>76</v>
-      </c>
-      <c r="E106" t="s">
-        <v>73</v>
-      </c>
-      <c r="F106" t="s">
-        <v>74</v>
-      </c>
-      <c r="G106" t="s">
-        <v>91</v>
-      </c>
-      <c r="I106" t="s">
-        <v>28</v>
-      </c>
-      <c r="J106" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="107" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A107" t="s">
-        <v>71</v>
-      </c>
-      <c r="B107" t="s">
-        <v>72</v>
-      </c>
-      <c r="C107" t="s">
-        <v>75</v>
-      </c>
-      <c r="D107" t="s">
-        <v>76</v>
-      </c>
-      <c r="E107" t="s">
-        <v>83</v>
-      </c>
-      <c r="F107" t="s">
-        <v>84</v>
-      </c>
-      <c r="G107" t="s">
-        <v>91</v>
-      </c>
-      <c r="I107" t="s">
-        <v>43</v>
-      </c>
-      <c r="J107" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="108" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A108" t="s">
-        <v>71</v>
-      </c>
-      <c r="B108" t="s">
-        <v>72</v>
-      </c>
-      <c r="C108" t="s">
-        <v>77</v>
-      </c>
-      <c r="D108" t="s">
-        <v>78</v>
-      </c>
-      <c r="E108" t="s">
-        <v>87</v>
-      </c>
-      <c r="F108" t="s">
-        <v>88</v>
-      </c>
-      <c r="G108" t="s">
+      <c r="D112" t="s">
         <v>92</v>
-      </c>
-      <c r="I108" t="s">
-        <v>48</v>
-      </c>
-      <c r="J108" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="109" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A109" t="s">
-        <v>71</v>
-      </c>
-      <c r="B109" t="s">
-        <v>72</v>
-      </c>
-      <c r="C109" t="s">
-        <v>77</v>
-      </c>
-      <c r="D109" t="s">
-        <v>78</v>
-      </c>
-      <c r="E109" t="s">
-        <v>81</v>
-      </c>
-      <c r="F109" t="s">
-        <v>82</v>
-      </c>
-      <c r="G109" t="s">
-        <v>92</v>
-      </c>
-      <c r="I109" t="s">
-        <v>37</v>
-      </c>
-      <c r="J109" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="110" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A110" t="s">
-        <v>71</v>
-      </c>
-      <c r="B110" t="s">
-        <v>72</v>
-      </c>
-      <c r="C110" t="s">
-        <v>77</v>
-      </c>
-      <c r="D110" t="s">
-        <v>78</v>
-      </c>
-      <c r="E110" t="s">
-        <v>75</v>
-      </c>
-      <c r="F110" t="s">
-        <v>76</v>
-      </c>
-      <c r="G110" t="s">
-        <v>92</v>
-      </c>
-      <c r="I110" t="s">
-        <v>25</v>
-      </c>
-      <c r="J110" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="111" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A111" t="s">
-        <v>71</v>
-      </c>
-      <c r="B111" t="s">
-        <v>72</v>
-      </c>
-      <c r="C111" t="s">
-        <v>77</v>
-      </c>
-      <c r="D111" t="s">
-        <v>78</v>
-      </c>
-      <c r="E111" t="s">
-        <v>85</v>
-      </c>
-      <c r="F111" t="s">
-        <v>86</v>
-      </c>
-      <c r="G111" t="s">
-        <v>92</v>
-      </c>
-      <c r="I111" t="s">
-        <v>18</v>
-      </c>
-      <c r="J111" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="112" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A112" t="s">
-        <v>71</v>
-      </c>
-      <c r="B112" t="s">
-        <v>72</v>
-      </c>
-      <c r="C112" t="s">
-        <v>77</v>
-      </c>
-      <c r="D112" t="s">
-        <v>78</v>
       </c>
       <c r="E112" t="s">
         <v>83</v>
@@ -3844,7 +3856,10 @@
         <v>84</v>
       </c>
       <c r="G112" t="s">
-        <v>92</v>
+        <v>66</v>
+      </c>
+      <c r="H112" t="s">
+        <v>67</v>
       </c>
       <c r="I112" t="s">
         <v>28</v>
@@ -3853,88 +3868,97 @@
         <v>19</v>
       </c>
     </row>
-    <row r="113" x14ac:dyDescent="0.25" spans="1:9">
+    <row r="113" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A113" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B113" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C113" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D113" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E113" t="s">
+        <v>74</v>
+      </c>
+      <c r="F113" t="s">
+        <v>75</v>
+      </c>
+      <c r="G113" t="s">
+        <v>66</v>
+      </c>
+      <c r="H113" t="s">
+        <v>67</v>
+      </c>
+      <c r="I113" t="s">
+        <v>34</v>
+      </c>
+      <c r="J113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A114" t="s">
+        <v>72</v>
+      </c>
+      <c r="B114" t="s">
+        <v>73</v>
+      </c>
+      <c r="C114" t="s">
+        <v>91</v>
+      </c>
+      <c r="D114" t="s">
+        <v>92</v>
+      </c>
+      <c r="E114" t="s">
         <v>79</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F114" t="s">
         <v>80</v>
       </c>
-      <c r="G113" t="s">
+      <c r="G114" t="s">
+        <v>66</v>
+      </c>
+      <c r="H114" t="s">
+        <v>67</v>
+      </c>
+      <c r="I114" t="s">
+        <v>47</v>
+      </c>
+      <c r="J114" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" x14ac:dyDescent="0.25" spans="1:10">
+      <c r="A115" t="s">
+        <v>72</v>
+      </c>
+      <c r="B115" t="s">
+        <v>73</v>
+      </c>
+      <c r="C115" t="s">
+        <v>91</v>
+      </c>
+      <c r="D115" t="s">
         <v>92</v>
       </c>
-      <c r="I113" t="s">
-        <v>43</v>
-      </c>
-      <c r="J113" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="114" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A114" t="s">
-        <v>71</v>
-      </c>
-      <c r="B114" t="s">
-        <v>72</v>
-      </c>
-      <c r="C114" t="s">
-        <v>77</v>
-      </c>
-      <c r="D114" t="s">
-        <v>78</v>
-      </c>
-      <c r="E114" t="s">
-        <v>73</v>
-      </c>
-      <c r="F114" t="s">
-        <v>74</v>
-      </c>
-      <c r="G114" t="s">
-        <v>92</v>
-      </c>
-      <c r="I114" t="s">
-        <v>31</v>
-      </c>
-      <c r="J114" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="115" x14ac:dyDescent="0.25" spans="1:9">
-      <c r="A115" t="s">
-        <v>71</v>
-      </c>
-      <c r="B115" t="s">
-        <v>72</v>
-      </c>
-      <c r="C115" t="s">
-        <v>77</v>
-      </c>
-      <c r="D115" t="s">
-        <v>78</v>
-      </c>
       <c r="E115" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F115" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G115" t="s">
-        <v>92</v>
+        <v>66</v>
+      </c>
+      <c r="H115" t="s">
+        <v>67</v>
       </c>
       <c r="I115" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J115" t="s">
         <v>19</v>
@@ -3942,31 +3966,31 @@
     </row>
     <row r="116" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A116" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B116" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C116" t="s">
+        <v>79</v>
+      </c>
+      <c r="D116" t="s">
+        <v>80</v>
+      </c>
+      <c r="E116" t="s">
         <v>83</v>
       </c>
-      <c r="D116" t="s">
+      <c r="F116" t="s">
         <v>84</v>
       </c>
-      <c r="E116" t="s">
-        <v>75</v>
-      </c>
-      <c r="F116" t="s">
-        <v>76</v>
-      </c>
       <c r="G116" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H116" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I116" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="J116" t="s">
         <v>19</v>
@@ -3974,31 +3998,31 @@
     </row>
     <row r="117" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A117" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B117" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C117" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D117" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E117" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F117" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G117" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H117" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I117" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="J117" t="s">
         <v>19</v>
@@ -4006,31 +4030,31 @@
     </row>
     <row r="118" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A118" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B118" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C118" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D118" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E118" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F118" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="G118" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H118" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I118" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="J118" t="s">
         <v>19</v>
@@ -4038,31 +4062,31 @@
     </row>
     <row r="119" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A119" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B119" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C119" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D119" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E119" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F119" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G119" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H119" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I119" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J119" t="s">
         <v>19</v>
@@ -4070,31 +4094,31 @@
     </row>
     <row r="120" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A120" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B120" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C120" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D120" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E120" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F120" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="G120" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H120" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I120" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J120" t="s">
         <v>19</v>
@@ -4102,31 +4126,31 @@
     </row>
     <row r="121" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A121" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B121" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C121" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D121" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E121" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F121" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G121" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H121" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I121" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="J121" t="s">
         <v>19</v>
@@ -4134,31 +4158,31 @@
     </row>
     <row r="122" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A122" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B122" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C122" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D122" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E122" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F122" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G122" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H122" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I122" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J122" t="s">
         <v>19</v>
@@ -4166,31 +4190,31 @@
     </row>
     <row r="123" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A123" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B123" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C123" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D123" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E123" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F123" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G123" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H123" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I123" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J123" t="s">
         <v>19</v>
@@ -4198,31 +4222,31 @@
     </row>
     <row r="124" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A124" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B124" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C124" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D124" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E124" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F124" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G124" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H124" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I124" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J124" t="s">
         <v>19</v>
@@ -4230,31 +4254,31 @@
     </row>
     <row r="125" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A125" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B125" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C125" t="s">
+        <v>81</v>
+      </c>
+      <c r="D125" t="s">
+        <v>82</v>
+      </c>
+      <c r="E125" t="s">
         <v>85</v>
       </c>
-      <c r="D125" t="s">
+      <c r="F125" t="s">
         <v>86</v>
       </c>
-      <c r="E125" t="s">
-        <v>83</v>
-      </c>
-      <c r="F125" t="s">
-        <v>84</v>
-      </c>
       <c r="G125" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H125" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I125" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J125" t="s">
         <v>19</v>
@@ -4262,31 +4286,31 @@
     </row>
     <row r="126" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A126" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B126" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C126" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D126" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E126" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F126" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G126" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H126" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I126" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J126" t="s">
         <v>19</v>
@@ -4294,31 +4318,31 @@
     </row>
     <row r="127" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A127" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B127" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C127" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D127" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E127" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F127" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G127" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H127" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I127" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="J127" t="s">
         <v>19</v>
@@ -4326,28 +4350,28 @@
     </row>
     <row r="128" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A128" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B128" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C128" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D128" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E128" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F128" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G128" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H128" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I128" t="s">
         <v>46</v>
@@ -4358,28 +4382,28 @@
     </row>
     <row r="129" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A129" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B129" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C129" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D129" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E129" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F129" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G129" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H129" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I129" t="s">
         <v>40</v>
@@ -4390,31 +4414,31 @@
     </row>
     <row r="130" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A130" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B130" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C130" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D130" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E130" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F130" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G130" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H130" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I130" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="J130" t="s">
         <v>19</v>
@@ -4422,31 +4446,31 @@
     </row>
     <row r="131" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A131" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B131" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C131" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D131" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E131" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F131" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G131" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H131" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I131" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="J131" t="s">
         <v>19</v>
@@ -4454,28 +4478,28 @@
     </row>
     <row r="132" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A132" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B132" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C132" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D132" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E132" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F132" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G132" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H132" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I132" t="s">
         <v>22</v>
@@ -4486,31 +4510,31 @@
     </row>
     <row r="133" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A133" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B133" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C133" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D133" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E133" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F133" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G133" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H133" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I133" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J133" t="s">
         <v>19</v>
@@ -4518,28 +4542,28 @@
     </row>
     <row r="134" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A134" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C134" t="s">
+        <v>85</v>
+      </c>
+      <c r="D134" t="s">
+        <v>86</v>
+      </c>
+      <c r="E134" t="s">
         <v>87</v>
       </c>
-      <c r="D134" t="s">
+      <c r="F134" t="s">
         <v>88</v>
       </c>
-      <c r="E134" t="s">
-        <v>89</v>
-      </c>
-      <c r="F134" t="s">
-        <v>90</v>
-      </c>
       <c r="G134" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H134" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I134" t="s">
         <v>18</v>
@@ -4550,31 +4574,31 @@
     </row>
     <row r="135" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A135" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B135" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C135" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D135" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E135" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F135" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G135" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H135" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I135" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J135" t="s">
         <v>19</v>
@@ -4582,31 +4606,31 @@
     </row>
     <row r="136" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A136" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B136" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C136" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D136" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E136" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F136" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G136" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H136" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I136" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J136" t="s">
         <v>19</v>
@@ -4614,31 +4638,31 @@
     </row>
     <row r="137" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A137" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B137" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C137" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D137" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E137" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F137" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G137" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H137" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I137" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="J137" t="s">
         <v>19</v>
@@ -4646,31 +4670,31 @@
     </row>
     <row r="138" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A138" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B138" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C138" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D138" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E138" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="F138" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="G138" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H138" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I138" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="J138" t="s">
         <v>19</v>
@@ -4678,31 +4702,31 @@
     </row>
     <row r="139" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A139" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B139" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C139" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D139" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E139" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F139" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G139" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H139" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I139" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J139" t="s">
         <v>19</v>
@@ -4710,16 +4734,16 @@
     </row>
     <row r="140" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A140" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B140" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C140" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D140" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E140" t="s">
         <v>87</v>
@@ -4728,10 +4752,10 @@
         <v>88</v>
       </c>
       <c r="G140" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I140" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J140" t="s">
         <v>19</v>
@@ -4739,25 +4763,25 @@
     </row>
     <row r="141" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A141" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B141" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C141" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D141" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E141" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F141" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G141" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I141" t="s">
         <v>28</v>
@@ -4768,28 +4792,28 @@
     </row>
     <row r="142" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A142" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B142" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C142" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D142" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E142" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F142" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G142" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I142" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J142" t="s">
         <v>19</v>
@@ -4797,28 +4821,28 @@
     </row>
     <row r="143" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A143" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B143" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C143" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D143" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E143" t="s">
+        <v>74</v>
+      </c>
+      <c r="F143" t="s">
         <v>75</v>
       </c>
-      <c r="F143" t="s">
-        <v>76</v>
-      </c>
       <c r="G143" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I143" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="J143" t="s">
         <v>19</v>
@@ -4826,28 +4850,28 @@
     </row>
     <row r="144" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A144" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B144" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C144" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D144" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E144" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F144" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G144" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I144" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J144" t="s">
         <v>19</v>
@@ -4855,28 +4879,28 @@
     </row>
     <row r="145" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A145" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B145" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C145" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D145" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E145" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F145" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G145" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I145" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J145" t="s">
         <v>19</v>
@@ -4884,28 +4908,28 @@
     </row>
     <row r="146" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A146" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B146" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C146" t="s">
+        <v>76</v>
+      </c>
+      <c r="D146" t="s">
+        <v>77</v>
+      </c>
+      <c r="E146" t="s">
         <v>81</v>
       </c>
-      <c r="D146" t="s">
+      <c r="F146" t="s">
         <v>82</v>
       </c>
-      <c r="E146" t="s">
-        <v>83</v>
-      </c>
-      <c r="F146" t="s">
-        <v>84</v>
-      </c>
       <c r="G146" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I146" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J146" t="s">
         <v>19</v>
@@ -4913,28 +4937,28 @@
     </row>
     <row r="147" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A147" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B147" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C147" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D147" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E147" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F147" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G147" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I147" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="J147" t="s">
         <v>19</v>
@@ -4942,31 +4966,31 @@
     </row>
     <row r="148" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A148" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B148" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C148" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D148" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E148" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F148" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G148" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H148" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I148" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J148" t="s">
         <v>19</v>
@@ -4974,31 +4998,31 @@
     </row>
     <row r="149" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B149" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C149" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D149" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E149" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F149" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="G149" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H149" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I149" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="J149" t="s">
         <v>19</v>
@@ -5006,31 +5030,31 @@
     </row>
     <row r="150" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A150" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C150" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D150" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E150" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F150" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G150" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H150" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I150" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J150" t="s">
         <v>19</v>
@@ -5038,16 +5062,16 @@
     </row>
     <row r="151" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A151" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B151" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C151" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D151" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E151" t="s">
         <v>83</v>
@@ -5056,10 +5080,10 @@
         <v>84</v>
       </c>
       <c r="G151" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H151" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I151" t="s">
         <v>47</v>
@@ -5070,31 +5094,31 @@
     </row>
     <row r="152" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A152" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B152" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C152" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D152" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E152" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="F152" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G152" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H152" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I152" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J152" t="s">
         <v>19</v>
@@ -5102,16 +5126,16 @@
     </row>
     <row r="153" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A153" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B153" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C153" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D153" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E153" t="s">
         <v>85</v>
@@ -5120,13 +5144,13 @@
         <v>86</v>
       </c>
       <c r="G153" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H153" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I153" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="J153" t="s">
         <v>19</v>
@@ -5134,31 +5158,31 @@
     </row>
     <row r="154" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A154" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B154" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C154" t="s">
+        <v>87</v>
+      </c>
+      <c r="D154" t="s">
+        <v>88</v>
+      </c>
+      <c r="E154" t="s">
         <v>79</v>
       </c>
-      <c r="D154" t="s">
+      <c r="F154" t="s">
         <v>80</v>
       </c>
-      <c r="E154" t="s">
-        <v>81</v>
-      </c>
-      <c r="F154" t="s">
-        <v>82</v>
-      </c>
       <c r="G154" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H154" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I154" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J154" t="s">
         <v>19</v>
@@ -5166,42 +5190,42 @@
     </row>
     <row r="155" x14ac:dyDescent="0.25" spans="1:10">
       <c r="A155" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B155" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C155" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D155" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E155" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="F155" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="G155" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H155" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I155" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="J155" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="156" x14ac:dyDescent="0.25" spans="1:10">
+    <row r="156" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A156" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B156" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C156" t="s">
         <v>89</v>
@@ -5210,30 +5234,27 @@
         <v>90</v>
       </c>
       <c r="E156" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F156" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G156" t="s">
-        <v>103</v>
-      </c>
-      <c r="H156" t="s">
         <v>104</v>
       </c>
       <c r="I156" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J156" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="157" x14ac:dyDescent="0.25" spans="1:10">
+    <row r="157" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A157" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B157" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C157" t="s">
         <v>89</v>
@@ -5242,30 +5263,27 @@
         <v>90</v>
       </c>
       <c r="E157" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F157" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G157" t="s">
-        <v>103</v>
-      </c>
-      <c r="H157" t="s">
         <v>104</v>
       </c>
       <c r="I157" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="J157" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="158" x14ac:dyDescent="0.25" spans="1:10">
+    <row r="158" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A158" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B158" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C158" t="s">
         <v>89</v>
@@ -5274,30 +5292,27 @@
         <v>90</v>
       </c>
       <c r="E158" t="s">
+        <v>74</v>
+      </c>
+      <c r="F158" t="s">
         <v>75</v>
       </c>
-      <c r="F158" t="s">
-        <v>76</v>
-      </c>
       <c r="G158" t="s">
-        <v>103</v>
-      </c>
-      <c r="H158" t="s">
         <v>104</v>
       </c>
       <c r="I158" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J158" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="159" x14ac:dyDescent="0.25" spans="1:10">
+    <row r="159" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A159" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B159" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C159" t="s">
         <v>89</v>
@@ -5306,30 +5321,27 @@
         <v>90</v>
       </c>
       <c r="E159" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F159" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G159" t="s">
-        <v>103</v>
-      </c>
-      <c r="H159" t="s">
         <v>104</v>
       </c>
       <c r="I159" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="J159" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="160" x14ac:dyDescent="0.25" spans="1:10">
+    <row r="160" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A160" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B160" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C160" t="s">
         <v>89</v>
@@ -5344,24 +5356,21 @@
         <v>84</v>
       </c>
       <c r="G160" t="s">
-        <v>103</v>
-      </c>
-      <c r="H160" t="s">
         <v>104</v>
       </c>
       <c r="I160" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J160" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="161" x14ac:dyDescent="0.25" spans="1:10">
+    <row r="161" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A161" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B161" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C161" t="s">
         <v>89</v>
@@ -5376,24 +5385,21 @@
         <v>80</v>
       </c>
       <c r="G161" t="s">
-        <v>103</v>
-      </c>
-      <c r="H161" t="s">
         <v>104</v>
       </c>
       <c r="I161" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J161" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="162" x14ac:dyDescent="0.25" spans="1:10">
+    <row r="162" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A162" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B162" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C162" t="s">
         <v>89</v>
@@ -5408,24 +5414,21 @@
         <v>86</v>
       </c>
       <c r="G162" t="s">
-        <v>103</v>
-      </c>
-      <c r="H162" t="s">
         <v>104</v>
       </c>
       <c r="I162" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J162" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="163" x14ac:dyDescent="0.25" spans="1:10">
+    <row r="163" x14ac:dyDescent="0.25" spans="1:9">
       <c r="A163" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B163" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C163" t="s">
         <v>89</v>
@@ -5434,19 +5437,16 @@
         <v>90</v>
       </c>
       <c r="E163" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F163" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G163" t="s">
-        <v>103</v>
-      </c>
-      <c r="H163" t="s">
         <v>104</v>
       </c>
       <c r="I163" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="J163" t="s">
         <v>19</v>
